--- a/artfynd/A 64875-2021 artfynd.xlsx
+++ b/artfynd/A 64875-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126233240</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126233916</v>
       </c>
       <c r="B4" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126233881</v>
       </c>
       <c r="B5" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126233484</v>
       </c>
       <c r="B7" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64875-2021 artfynd.xlsx
+++ b/artfynd/A 64875-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126233240</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126232063</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126233916</v>
       </c>
       <c r="B4" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126233881</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126231793</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126233484</v>
       </c>
       <c r="B7" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64875-2021 artfynd.xlsx
+++ b/artfynd/A 64875-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126233240</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126233916</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126233881</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126233484</v>
       </c>
       <c r="B7" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64875-2021 artfynd.xlsx
+++ b/artfynd/A 64875-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126233240</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126232063</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126233916</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126233881</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126231793</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126233484</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
